--- a/anhang/umfrage-Ergebnisse.xlsx
+++ b/anhang/umfrage-Ergebnisse.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benedikt.mehl/Documents/master-thesis/anhang/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D183887E-707A-E645-AE30-7156D6158AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="19900" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="228">
   <si>
     <t>Index</t>
   </si>
@@ -643,13 +648,82 @@
   </si>
   <si>
     <t>116</t>
+  </si>
+  <si>
+    <t>09/12 2025 08:30:39 PM (UTC+02:00) Central European Time (Berlin)</t>
+  </si>
+  <si>
+    <t>3014s</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>104.23.239.16(Unknown/United States)</t>
+  </si>
+  <si>
+    <t>Software-Visualisierungen sind besonders hilfreich, um große Codebasen anhand verschiedener Metriken nachvollziehbar zu machen. Allerdings sollten sie nicht zu viele Details enthalten, da sonst der Überblick verloren geht. Richtig eingesetzt, können sie komplexen Code deutlich zugänglicher machen.</t>
+  </si>
+  <si>
+    <t>Das Baumstruktur-Diagramm war für die Analyse der Dateianzahl in den Ordnern verständlich, aber sonst war die Darstellung eher unübersichtlich bzw. eher nicht intuitiv.</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>09/16 2025 10:48:18 AM (UTC+02:00) Central European Time (Berlin)</t>
+  </si>
+  <si>
+    <t>989s</t>
+  </si>
+  <si>
+    <t>172.71.195.17(Ashburn/Virginia/United States)</t>
+  </si>
+  <si>
+    <t>Ich finde sie generell sinnvoll, um einen schnellen Eindruck über verschiedene Metriken gewinnen zu können. Imho denken viele Menschen vorwiegend visuell, also ist eine Datenvisualisierung sinnvoll.</t>
+  </si>
+  <si>
+    <t>An manchen Stellen konnte ich den Text nicht gut lesen, und bei der einen Visualisierung konnte ich überhaupt nicht erkennen, dass transport_by_car nicht in transport liegt. Im Gegenteil: Es sah so aus, als sei es Teil des Ordners.</t>
+  </si>
+  <si>
+    <t>Ich gehe davon aus, dass es möglich ist, die Visualisierungen wie ein 3D-Objekt zu nutzen und zu zoomen / schwenken etc... (?). In dem Falle würde ich jede einzelne Visualisierung etwas besser bewerten.</t>
+  </si>
+  <si>
+    <t>09/17 2025 01:26:59 PM (UTC+02:00) Central European Time (Berlin)</t>
+  </si>
+  <si>
+    <t>1502s</t>
+  </si>
+  <si>
+    <t>194.233.100.146(Seattle/Washington/United States)</t>
+  </si>
+  <si>
+    <t>Ja sie sind sinnvoll. Sie verschaffen einen schnellen Überblick und beschleunigen das Erkennen von Trends</t>
+  </si>
+  <si>
+    <t>Die baumartige visualisierung hat sehr viel freien Platz. Der Text ist sehr klein und schwierig überhaupt zu finden. Man braucht zu lange um sich dort zu orientieren. 
+Die quadratischen Visualisierungen die den gesamten Platz ausnutzen sind an sich gut, aber manchmal ist es schwierig die Höhe zu interpretieren und es besteht die Gefahr, dass Text verdeckt wird.</t>
+  </si>
+  <si>
+    <t>115</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -658,7 +732,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -673,110 +747,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Comma" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Comma [0]" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Currency" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Currency [0]" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1099,11 +1098,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV19"/>
-  <sheetFormatPr defaultColWidth="9.142857142857142" defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BV22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:74" ht="12.75">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1327,7 +1330,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:74" ht="12.75">
+    <row r="2" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1551,7 +1554,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:74" ht="12.75">
+    <row r="3" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -1775,7 +1778,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:74" ht="12.75">
+    <row r="4" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -1999,7 +2002,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:74" ht="12.75">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -2223,7 +2226,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:74" ht="12.75">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>116</v>
       </c>
@@ -2447,7 +2450,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:74" ht="12.75">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -2671,7 +2674,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:74" ht="12.75">
+    <row r="8" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -2895,7 +2898,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:74" ht="12.75">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>138</v>
       </c>
@@ -3119,7 +3122,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:74" ht="12.75">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>146</v>
       </c>
@@ -3343,7 +3346,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:74" ht="12.75">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -3567,7 +3570,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:74" ht="12.75">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>159</v>
       </c>
@@ -3791,7 +3794,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:74" ht="12.75">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -4015,7 +4018,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:74" ht="12.75">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>170</v>
       </c>
@@ -4239,7 +4242,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:74" ht="12.75">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>177</v>
       </c>
@@ -4463,7 +4466,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:74" ht="12.75">
+    <row r="16" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -4687,7 +4690,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:74" ht="12.75">
+    <row r="17" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -4911,7 +4914,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:74" ht="12.75">
+    <row r="18" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>167</v>
       </c>
@@ -5135,7 +5138,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:74" ht="12.75">
+    <row r="19" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>204</v>
       </c>
@@ -5357,10 +5360,682 @@
       </c>
       <c r="BV19" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:74" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>211</v>
+      </c>
+      <c r="F20" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L20" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" t="s">
+        <v>83</v>
+      </c>
+      <c r="N20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O20" t="s">
+        <v>82</v>
+      </c>
+      <c r="P20" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" t="s">
+        <v>83</v>
+      </c>
+      <c r="S20" t="s">
+        <v>83</v>
+      </c>
+      <c r="T20" t="s">
+        <v>84</v>
+      </c>
+      <c r="U20" t="s">
+        <v>83</v>
+      </c>
+      <c r="V20" t="s">
+        <v>83</v>
+      </c>
+      <c r="W20" t="s">
+        <v>84</v>
+      </c>
+      <c r="X20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>85</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>85</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>84</v>
+      </c>
+      <c r="BS20" t="s">
+        <v>213</v>
+      </c>
+      <c r="BT20" t="s">
+        <v>214</v>
+      </c>
+      <c r="BU20" t="s">
+        <v>93</v>
+      </c>
+      <c r="BV20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:74" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" t="s">
+        <v>218</v>
+      </c>
+      <c r="G21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M21" t="s">
+        <v>83</v>
+      </c>
+      <c r="N21" t="s">
+        <v>83</v>
+      </c>
+      <c r="O21" t="s">
+        <v>82</v>
+      </c>
+      <c r="P21" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>84</v>
+      </c>
+      <c r="R21" t="s">
+        <v>83</v>
+      </c>
+      <c r="S21" t="s">
+        <v>82</v>
+      </c>
+      <c r="T21" t="s">
+        <v>83</v>
+      </c>
+      <c r="U21" t="s">
+        <v>85</v>
+      </c>
+      <c r="V21" t="s">
+        <v>85</v>
+      </c>
+      <c r="W21" t="s">
+        <v>83</v>
+      </c>
+      <c r="X21" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>89</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>105</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>85</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BJ21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BO21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BQ21" t="s">
+        <v>105</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS21" t="s">
+        <v>219</v>
+      </c>
+      <c r="BT21" t="s">
+        <v>220</v>
+      </c>
+      <c r="BU21" t="s">
+        <v>221</v>
+      </c>
+      <c r="BV21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:74" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" t="s">
+        <v>223</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" t="s">
+        <v>84</v>
+      </c>
+      <c r="M22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" t="s">
+        <v>83</v>
+      </c>
+      <c r="O22" t="s">
+        <v>83</v>
+      </c>
+      <c r="P22" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>89</v>
+      </c>
+      <c r="R22" t="s">
+        <v>82</v>
+      </c>
+      <c r="S22" t="s">
+        <v>83</v>
+      </c>
+      <c r="T22" t="s">
+        <v>83</v>
+      </c>
+      <c r="U22" t="s">
+        <v>83</v>
+      </c>
+      <c r="V22" t="s">
+        <v>83</v>
+      </c>
+      <c r="W22" t="s">
+        <v>89</v>
+      </c>
+      <c r="X22" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB22" t="s">
+        <v>105</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG22" t="s">
+        <v>168</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>168</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>85</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>168</v>
+      </c>
+      <c r="BN22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BO22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BP22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BQ22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BR22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BS22" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT22" t="s">
+        <v>226</v>
+      </c>
+      <c r="BU22" t="s">
+        <v>93</v>
+      </c>
+      <c r="BV22" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>